--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_003/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_003/extracted.xlsx
@@ -279,6 +279,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -350,21 +355,6 @@
       </text>
     </comment>
     <comment ref="D6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1301,12 +1291,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Structural credibility assessment of Ti-6Al-4V L-bracket for HALO rack avionics mounting under launch and on-orbit vibration</t>
+          <t>Structural qualification of Ti-6Al-4V L-bracket for HALO rack EPS avionics mount under launch and on-orbit vibration</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Finite element analysis of the HALO EPS avionics box mounting bracket (Ti-6Al-4V, 4.0 mm plate) to predict modal frequencies, RMS stress hotspots at fillets and bolt pads, and fastener joint slip under random vibration PSD loading. Results used to establish qualification and protoflight margins prior to CDR.</t>
+          <t>Linear modal, random vibration (PSD), and static FEA of a Ti-6Al-4V L-shaped bracket mounting an electronics box to the HALO rack. Context of use is to determine whether hotspot stresses at filleted corners and bolt pads remain below allowable, whether first three natural frequencies clear payload tone bands by ≥10%, and whether fastener clamp load is maintained with negligible joint slip under qualification-level random vibration (9.0 g RMS, 20–2000 Hz).</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1340,9 +1330,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (Gateway Avionics Mount Bracket FEA — Credibility Slide Deck, Rev C)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1403,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1461,7 +1451,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Structural Margin and Frequency Separation Requirements</t>
+          <t>Structural Qualification Requirements for HALO Avionics Bracket</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1471,7 +1461,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>First three modes must be clear of payload tone bands by ≥10%; peak 3σ von Mises stress must remain below Ti-6Al-4V yield; fastener slip safety factor must be ≥1.4; model-to-test frequency agreement must be within 10% for first three modes.</t>
+          <t>Hotspot stresses must remain below Ti-6Al-4V allowable; first three natural frequencies must clear payload tone bands by ≥10%; bolt slip safety factor must be ≥1.4; load environment is 9.0 g RMS flat PSD 80–350 Hz.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1493,12 +1483,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Ansys Mechanical 2023 R2 FEA Model — HALO-AV-BRKT</t>
+          <t>Ansys Mechanical 2023 R2 FEA Model — Bracket Assembly</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Linear modal, random vibration PSD, and static FEA of Ti-6Al-4V L-bracket using 10-node tetrahedral elements (SOLID187), beam bolt elements with pretension, and frictional contact at bracket interfaces.</t>
+          <t>Linear modal and random vibration FEA of HALO-PWR-AV-BRKT-1203 Rev H geometry using 10-node tetrahedral elements, frictional contact, beam bolt elements with pretension, and bilinear Ti-6Al-4V material.</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1505,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Sine-sweep and random vibration test data from 6 accelerometers and 2 strain gauges on the development bracket with mass simulator; provides measured modal frequencies and RMS strains for model correlation.</t>
+          <t>Fixed-base sine sweep (6 accelerometers, 2 strain gauges) and random vibration test data providing modal frequencies and RMS strain at fillet F2 for model correlation.</t>
         </is>
       </c>
     </row>
@@ -1532,24 +1522,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Elastic modulus, yield strength, and bilinear hardening parameters from MMPDS-17 handbook and internal coupon test ATB-0423; conflicting values (E = 110 vs 114 GPa; σy = 880 vs 930 MPa) are unresolved in the current model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>PSD Load Specification — Launch Vibration Environment</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Random vibration input PSD spectrum (20–2000 Hz, 0.05 g²/Hz flat 80–350 Hz); specified overall level is 9.0 g RMS, but the production model input file encodes 7.5 g RMS — discrepancy unresolved.</t>
+          <t>Elastic moduli, yield strength, and bilinear hardening data from MMPDS-17 (room temperature) and internal coupon test ATB-0423; conflicting values present between sources and solver libraries.</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1959,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study</t>
+          <t>Modal Frequency Correlation — Sine Sweep Test</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2001,12 +1974,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Three nested meshes (Coarse ~220k DOF, Medium ~680k DOF, Fine ~1.45M DOF) compared for first modal frequency and RMS von Mises stress at fillet F2. Medium-to-Fine changes reported as ≤2% for primary QoIs in Ansys; however, bolt pad hotspot P3 shows +7.4% change in an Abaqus cross-solver run. Final production runs use Medium mesh.</t>
+          <t>Fixed-base sine sweep on development bracket Rev F compared measured natural frequencies for first three modes against FEA predictions using Ansys Mechanical 2023 R2 medium mesh.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Self-convergence across mesh refinement levels</t>
+          <t>Shaker test sine sweep (development bracket Rev F, 6 accelerometers)</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2021,19 +1994,19 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>First mode: +1.6% (Med→Fine); RMS stress F2: +1.9% (Med→Fine); Hotspot P3: +7.4% (Abaqus run, cross-solver)</t>
+          <t>Mode 1: −4.1% (305 vs 318 Hz); Mode 2: −5.1% (486 vs 512 Hz); Mode 3: −12.2% (642 vs 731 Hz)</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Modal Frequency Correlation — Sine Sweep</t>
+          <t>RMS Strain Correlation — Random Vibration Test</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2043,12 +2016,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Fixed-base sine sweep test on development bracket Rev F compared modeled and measured natural frequencies for first three modes. Acceptance criterion was within 10% for all three modes.</t>
+          <t>Comparison of predicted RMS strain at strain gauge SG-2 near fillet F2 to measured value under random vibration excitation.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Shaker test sine-sweep measurements (accelerometers, development bracket Rev F)</t>
+          <t>Strain gauge SG-2 measurement on development bracket Rev F</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2058,19 +2031,19 @@
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Mode 1: −4.1% (305 vs 318 Hz); Mode 2: −5.1% (486 vs 512 Hz); Mode 3: −12.2% (642 vs 731 Hz)</t>
+          <t>Model 166 με vs Test 178 με (−6.7%); PSD peak at 340 Hz underpredicted by 14% at nominal damping</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Inconclusive</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Random Vibration RMS Strain Correlation</t>
+          <t>Mesh Convergence Study</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2080,12 +2053,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Comparison of model-predicted RMS strain at fillet location SG-2 to strain gauge measurement during random vibration test. PSD peak at 340 Hz also compared; 14% underprediction of PSD peak unless damping is adjusted to 1.5%.</t>
+          <t>Three nested meshes (coarse ~220k DOF, medium ~680k DOF, fine ~1.45M DOF) assessed for convergence of first natural frequency and RMS von Mises stress at fillet F2. Hotspot principal stress at bolt pad P3 showed 7.4% change (medium to fine) in a secondary solver run not reconciled with the primary solver.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Strain gauge SG-2 measurement during random vibration shaker test</t>
+          <t>Richardson extrapolation / GCI not performed; relative change between mesh levels reported</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2095,7 +2068,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>RMS strain: −6.7% (166 vs 178 με); PSD peak at 340 Hz: −14% (nominal damping)</t>
+          <t>Mode 1 change (medium→fine): +1.6%; RMS von Mises at F2: +1.9%; Bolt pad P3 principal stress (Abaqus run): +7.4%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2107,7 +2080,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Code Benchmark — Cantilever Beam and Patch Test</t>
+          <t>Code Benchmark — Patch Test and Cantilever Beam</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2117,7 +2090,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Simple cantilever beam reproduced closed-form deflection within 2.1% (run in Abaqus); patch test on bracket coupon submodel recovers uniform stress within 0.4%; rigid body mode check yields ~1e-6 Hz residual. Note: cantilever benchmark not repeated in Ansys production solver.</t>
+          <t>Patch test on coupon submodel recovers uniform stress within 0.4%; simple cantilever reproduces closed-form solution within 2.1%. Rigid body mode residuals ~1e-6 Hz. Cantilever benchmark run in Abaqus, not repeated in Ansys production solver.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -2132,7 +2105,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Cantilever: 2.1% error; Patch test: 0.4% error; RBM residual: ~1e-6 Hz</t>
+          <t>Patch test: 0.4% error; Cantilever: 2.1% error; Rigid body modes: ~1e-6 Hz</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2144,7 +2117,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>One-at-a-Time Sensitivity Sweeps</t>
+          <t>Parametric Sensitivity Sweeps</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2154,12 +2127,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Parametric sweeps on friction coefficient (μ = 0.1–0.3), pretension (±15%), and elastic modulus (110–114 GPa) to assess sensitivity of hotspot stress, joint slip reserve, and modal frequency. Monte Carlo and tolerance propagation not performed.</t>
+          <t>One-at-a-time sensitivity analysis varying friction coefficient (0.1–0.3), pretension (±15%), and elastic modulus (110–114 GPa) to characterize influence on hotspot stress, joint slip reserve, and first natural frequency.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Nominal model predictions</t>
+          <t>Nominal baseline model results</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2169,12 +2142,12 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>One-at-a-time parameter sweeps</t>
+          <t>One-at-a-time parameter variation (OAT)</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>μ sweep: hotspot stress −4% to +6%; pretension ±15%: slip reserve ±9%; E sweep: mode 1 shift +1.7%</t>
+          <t>μ variation: −4% to +6% on RMS hotspot stress; pretension ±15%: joint slip ±9%; E variation: mode 1 shift +1.7%</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2328,12 +2301,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA; version-controlled inputs; peer-reviewed model setup</t>
+          <t>Primary solver is a commercial code with documented quality processes; version traceability maintained for production runs.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys Mechanical 2023 R2 is a commercial solver with implied vendor QA. Python/PyANSYS scripts are stored in GitLab repo HALO-AV-BRKT with tag v0.9.3. However, the production random vibration .dat file has a hash mismatch to the tagged commit, meaning the exact production run is not fully traceable to version control. Peer review was limited to the preprocessor script only; no independent end-to-end rerun was performed. Abaqus 6.14 was used as secondary solver for two cases without documented QA cross-check. One reproduction step references an Abaqus plugin not present in the repo.</t>
+          <t>Ansys Mechanical 2023 R2 is a commercial solver with implicit quality processes. Scripts are stored in GitLab (HALO-AV-BRKT, tag v0.9.3). However, the production random vibration .dat file has a hash mismatch against the tagged commit, meaning the exact production input is not fully traceable. Abaqus 6.14 was used for secondary checks. Peer review covered only the preprocessor script; no end-to-end independent rerun was performed. An Abaqus plugin referenced in the README is not present in the repository.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2362,12 +2335,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Code verified against analytical solutions or benchmarks in the production solver</t>
+          <t>Code correctness demonstrated against analytical solutions or standard benchmarks within the primary production solver.</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>A cantilever beam benchmark achieved 2.1% agreement with closed-form solution and a patch test recovered uniform stress within 0.4%. Rigid body mode residuals are acceptably small (~1e-6 Hz). However, the cantilever benchmark was executed in Abaqus, not in the Ansys production solver, so direct code verification of Ansys Mechanical 2023 R2 against analytical solutions is not explicitly documented. No Method of Manufactured Solutions or additional benchmark problems are reported.</t>
+          <t>Patch test recovers uniform stress within 0.4%; rigid body mode residuals ~1e-6 Hz; cantilever beam matches closed form within 2.1%. However, the cantilever benchmark was run in Abaqus, not in the Ansys production solver, so direct code verification of Ansys for this model class is incomplete. No MMS or formal benchmark suite was applied in Ansys.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2396,12 +2369,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with &lt;5% change for primary QoIs across refinement levels; GCI or Richardson extrapolation reported</t>
+          <t>Mesh convergence demonstrated for all primary quantities of interest with &lt;5% change between successive refinements, or GCI computed.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>A three-level mesh refinement study was conducted (Coarse/Medium/Fine). For primary QoIs in Ansys, Medium-to-Fine changes are ≤2% for first mode and fillet F2 RMS stress. However, bolt pad hotspot P3 shows a +7.4% change in a cross-solver (Abaqus) run, casting doubt on convergence at that location. No GCI or Richardson extrapolation is reported. The fine mesh was not rerun with the latest boundary conditions. A linear-tet sensitivity run was performed but not used for final results. Contradictory caption on slide 9 ("Quadratic hex throughout") creates further ambiguity.</t>
+          <t>Three nested meshes were run (220k, 680k, 1.45M DOF). First mode and fillet F2 RMS stress show &lt;2% change from medium to fine in the Ansys runs. However, bolt pad P3 principal stress shows +7.4% change in the Abaqus cross-check run, which is unresolved. GCI or Richardson extrapolation was not computed. The production run used the medium mesh due to schedule pressure; the fine mesh was not rerun with final boundary conditions. The convergence plot omits the 7.4% outlier. These inconsistencies leave residual uncertainty in the hotspot location most critical to margin.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2430,12 +2403,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Solver residuals and convergence monitored; solver settings documented</t>
+          <t>Iterative solver convergence monitored; residual targets met; solver settings documented.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>The sparse direct solver in Ansys Mechanical 2023 R2 is documented (single precision, 16 cores, 128 GB RAM). Energy balance shows contact work fraction &lt;5% of total strain energy, indicating acceptable contact solution. Run wall times are recorded (1.3 hr modal, 3.8 hr random vib). No explicit residual convergence targets or iteration counts are reported for nonlinear contact iterations, but the direct solver choice inherently avoids iterative convergence concerns for the linear steps. Single precision is a minor concern for stress concentration accuracy.</t>
+          <t>Ansys sparse direct solver used (not iterative), so solver residual in the classical sense is not applicable. Rigid body mode check (residuals ~1e-6 Hz) and energy balance (contact work &lt;5% of total) serve as proxy convergence checks. Run metadata (cores, RAM, wall time) documented. Single precision noted for Ansys runs; potential precision loss for large models not explicitly assessed.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2464,12 +2437,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review of model setup, boundary conditions, and post-processing; mesh quality verified</t>
+          <t>Model setup independently reviewed end-to-end; boundary conditions verified against specification; mesh quality confirmed for final run.</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Design peer M. Patel reviewed the meshing strategy and boundary conditions checklist on 5/12. Element quality checks (Jacobian &gt;0.6, aspect ratio &lt;5) are documented. However, no independent end-to-end model rerun was performed. Multiple inconsistencies in model setup are present and unresolved: suppressed fillets in intermediate runs with images remaining in the deck; contradictory mesh descriptions (slide 9 caption vs actual elements used); load input discrepancy (7.5 vs 9.0 g RMS); conflicting material properties in solver vs reference. These unresolved inconsistencies indicate meaningful use-error risk.</t>
+          <t>Design peer M. Patel reviewed meshing strategy and boundary condition checklist on 5/12. However, no independent end-to-end model rebuild was performed (deferred to CDR). Several setup inconsistencies are documented: two stress plots show "&lt;1 mm fillets suppressed" (not final but images remain in the deck); slide 9 caption incorrectly states "Quadratic hex throughout" when this was true only for a submodel; PSD input in the model deck encodes 7.5 g RMS instead of the specified 9.0 g RMS; damping used in production differs from test-correlated value for mode 3; mass simulant (5.0 kg) differs from test (5.2 kg).</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2498,12 +2471,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and model type justified for the physics; known limitations documented</t>
+          <t>Physics model selection justified; governing equations appropriate for the load regimes; known limitations documented.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Linear modal and random vibration (PSD with Miles equivalent) analysis is appropriate for the described launch vibration regime. Frictional contact at interfaces is included. Known limitations are partially documented (Section 13): shock excluded, acoustic loads excluded, thermal-stress interaction excluded, plastic collapse not fully pursued. However, model form choices are not explicitly justified (e.g., no rationale for linear vs nonlinear modal, no turbulence or fluid physics relevant here but no discussion of geometric nonlinearity at fillet). The bilinear plasticity model is defined but not used in final margin calculations. Strain-rate effects are noted as excluded without justification.</t>
+          <t>Linear modal and random vibration analyses are appropriate for the qualification load regime. Bilinear plasticity is included for reference but not used for final margin calculations. Frictional contact with surface-to-surface formulation is applied. Limitations are partially documented: shock, acoustic, thermal-stress interaction, plastic collapse, micro-vib, and on-orbit creep are excluded with rationale. However, strain-rate effects are not included without justification, damping model is not physically motivated (assumed 1% then adjusted post-hoc to 1.5%), and the thermal gradient case (+50 K) affecting stresses is not carried into margin calculations despite shifting fillet stress by 5%.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2532,12 +2505,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties, loads, and boundary conditions from well-characterized sources with uncertainty noted</t>
+          <t>Material properties, boundary conditions, and loads traceable to authoritative sources; conflicts resolved; input uncertainties characterized.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Material data sourced from MMPDS-17 and internal coupon test ATB-0423, but conflicting values exist (E = 110 vs 114 GPa; σy = 880 vs 930 MPa) that are unresolved between the solver library and reference. PSD load level inconsistency (7.5 vs 9.0 g RMS) is unresolved. Friction coefficient μ = 0.2 is from a legacy trade study with no on-article measurement. Mass simulant is 5.2 kg in test vs 5.0 kg in model. Fastener pretension differs between build (5.5 N·m) and model (5.0 N·m equivalent). CAD mismatch (wire tie holes) assessed as negligible without quantification. Input uncertainties characterized only qualitatively through one-at-a-time sweeps; no formal UQ propagation performed.</t>
+          <t>Elastic modulus conflict: MMPDS-17 gives 114 GPa; Abaqus import uses 110 GPa "to be conservative" — inconsistency unresolved. Yield strength conflict: coupon ATB-0423 gives σy = 930 MPa; Ansys library screenshot shows 880 MPa — both values used in different parts of the report. PSD load level conflict: specification 9.0 g RMS vs model deck 7.5 g RMS — unresolved open item. Friction coefficient μ = 0.2 from legacy trade study with no on-article measurement. Mass simulant offset (5.0 vs 5.2 kg) not quantified. Pretension 5.0 N·m vs build 5.5 N·m. Wire tie holes omitted without quantification. CTE not used; thermal gradient effect not propagated to margins. Input conflicts represent a significant credibility gap.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2566,12 +2539,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article characterized and representative of the analysis subject</t>
+          <t>Test article is representative of the production configuration; sample count and configuration documented.</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>One development bracket (Rev F) with mass simulator was used for shaker testing. The report describes 6 accelerometers and 2 strain gauges. Only a single test article is described; no statistical characterization across multiple specimens is reported. The test article differs from the CAD model by revision (Rev F vs model based on later geometry) and by two additional wire tie holes. Sample size justification is absent.</t>
+          <t>One development bracket (Rev F) was used for shaker testing with a mass simulator. The report notes Rev F differs from the final geometry (two extra wire tie holes). Only a single test article is referenced; no statistical characterization across multiple specimens. The fixture resonance at 1,260 Hz was noted and accepted. Sample is pre-production, which limits direct applicability to the final bracket configuration.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2600,12 +2573,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions controlled and measured; calibration documented; fixture effects assessed</t>
+          <t>Test conditions controlled and measured; instrumentation calibrated; test standards referenced.</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Sine sweep and random vibration tests are described. A fixture resonance at 1,260 Hz was identified and accepted by the dynamics group. The PSD input spectrum is defined (20–2000 Hz, 0.05 g²/Hz flat 80–350 Hz, 9.0 g RMS overall). However, instrument calibration documentation is not referenced, measurement uncertainty for accelerometers and strain gauges is not reported, and controlled environmental conditions (temperature, humidity) during testing are not described. No reference to ASTM or ISO test standards.</t>
+          <t>Six accelerometers and two strain gauges used. Sine sweep and random vibration conducted at fixed-base configuration. Fixture resonance at 1,260 Hz noted by dynamics group. No calibration records, measurement uncertainty, or test standard (e.g., MIL-STD-810, ECSS) explicitly cited in the report. Damping derived post-hoc by adjusting model to match test peak rather than by direct measurement. Environmental controls not described.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2630,16 +2603,16 @@
         <v>3</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs match test conditions with differences quantified and assessed</t>
+          <t>Model inputs demonstrably match test article conditions; discrepancies quantified and their effect on outputs assessed.</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Several discrepancies between test article and model are identified but not all are quantified: mass simulant 5.2 kg (test) vs 5.0 kg (model); pretension 5.5 N·m (test) vs 5.0 N·m (model); wire tie holes present in test but absent in model (effect called negligible without analysis); friction coefficient assumed rather than measured. The damping discrepancy (1% assumed vs 1.5% needed to match 3rd mode) is identified but not reconciled in the final model. The PSD input level mismatch (7.5 vs 9.0 g RMS) directly affects pass/fail and is unresolved. No formal uncertainty propagation from input mismatches to QoI differences is performed.</t>
+          <t>Multiple unresolved discrepancies between model inputs and test conditions: PSD load level (7.5 g RMS in model vs 9.0 g RMS specification; test level not stated explicitly); mass simulant (5.0 kg model vs 5.2 kg test); pretension (5.0 N·m model vs 5.5 N·m build); two wire tie holes omitted from model (effect assessed as negligible without quantification); friction coefficient not measured on test article; test article Rev F differs geometrically from final bracket. No formal boundary condition matching matrix is presented. These discrepancies are acknowledged but not quantitatively reconciled.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2668,12 +2641,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to test measurements for primary QoIs; uncertainty bands reported</t>
+          <t>Quantitative comparison of model predictions to test data for all primary QoIs; stated acceptance criterion met.</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparisons are provided for modal frequencies (Mode 1: −4.1%, Mode 2: −5.1%, Mode 3: −12.2%) and RMS strain at SG-2 (−6.7%). PSD peak underprediction of 14% at 340 Hz is noted. The stated acceptance criterion of ±10% for first three modes is not met for Mode 3 (−12.2%), yet the slide 4 summary reports compliance — this is a documented inconsistency. No uncertainty bands on model predictions or test measurements are quantified. No statistical validation metrics (e.g., PEUR, u_val) are computed. Comparison is limited to two strain gauge locations and three modal frequencies.</t>
+          <t>Modal frequencies compared quantitatively: modes 1 and 2 within ~5% (borderline pass); mode 3 at −12.2% against a stated ±10% criterion — this is a documented failure that the slide 4 summary incorrectly characterizes as passing. RMS strain at SG-2: −6.7% (within 10%); PSD peak at 340 Hz underpredicted by 14% at nominal damping, requiring damping adjustment to 1.5% to match. No uncertainty bands are provided on either test or model outputs. Comparison is limited to one test article and two strain gauge locations. Bolt slip and hotspot stress are not directly validated against test measurements (no load cell or DIC data cited).</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2702,12 +2675,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly address the structural performance and safety questions posed</t>
+          <t>QoIs (hotspot stress, natural frequencies, bolt slip safety factor) are directly tied to the structural qualification decision and are measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>The QoIs (first three modal frequencies, RMS von Mises stress at fillet hotspots, fastener slip safety factor) directly correspond to the three primary engineering questions stated in Section 1: frequency separation from tone bands, structural stress margins, and fastener clamp load maintenance. These QoIs are measurable both computationally and experimentally (via accelerometers for frequency, strain gauges for stress, and analytical slip calculation). The connection between QoIs and pass/fail criteria is explicit, even though the criteria are not uniformly met.</t>
+          <t>The three primary QoIs — hotspot RMS stress at fillet F2 and bolt pad P3, natural frequencies of first three modes, and bolt slip safety factor — are directly relevant to the structural qualification decision (yield margin, tone band clearance, joint integrity). Natural frequencies and RMS strain are measurable experimentally and are compared to test data. Bolt slip and peak stress are computed from the validated model. The QoIs are well-defined and tied to specific pass/fail criteria in the analysis plan.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2736,12 +2709,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, loads, environment) match the intended qualification use</t>
+          <t>Validation tests cover the same geometry, material, load levels, and boundary conditions as the intended qualification use.</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation used a development bracket (Rev F) rather than the production/qualification configuration, with geometry differences (wire tie holes, potentially different fillet representation). The test article revision differs from the final CAD revision. The PSD load used in testing appears to be the correct 9.0 g RMS specification, but the production model encodes 7.5 g RMS — meaning validation correlation was not performed at the exact load level encoded in the final model. Shock, acoustic, and thermal-stress environments relevant to the full mission are excluded from both model and validation. On-orbit micro-vibration is explicitly excluded. These gaps limit the validation's coverage of the full qualification envelope.</t>
+          <t>Validation used a development bracket (Rev F) rather than the final production geometry. Test load level relationship to the 9.0 g RMS qualification environment is unclear (7.5 g RMS appears in the model deck). Damping was adjusted post-hoc to match test, rather than being independently characterized. Shock, acoustic, and thermal-stress environments are excluded from both model and validation. The on-orbit micro-vib environment is also excluded. The validation provides relevant modal and strain data but covers only a subset of the qualification envelope and uses a non-production test article, reducing applicability to the full COU.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2926,7 +2899,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The model is assessed as preliminary and not acceptable for finalizing qualification margins in its current state. Multiple unresolved inconsistencies directly affect the primary QoIs and pass/fail determinations: (1) the PSD load input discrepancy (7.5 vs 9.0 g RMS) is unresolved and affects all stress and slip results; (2) the 3rd modal frequency misses the stated ±10% acceptance criterion by 2.2 percentage points, yet the summary slide incorrectly claims compliance; (3) material property values (E and σy) are conflicting between the solver library and reference sources, creating ambiguity in both stress margins and modal predictions; (4) the production run has a hash mismatch to the version-controlled tag, undermining reproducibility; (5) the mesh convergence study shows a 7.4% hotspot change at bolt pad P3 in a cross-solver run that is not resolved in the Ansys production solver; (6) damping is inconsistent between assumption and test-derived value. The open items enumerated in Section 18 must be closed — particularly load level reconciliation, material property lock-down, full Ansys mesh convergence rerun, and a tagged reproducible production run — before the model can be accepted for qualification margin calculations.</t>
+          <t>The model is assessed as not acceptable in its current state for use in finalizing structural qualification margins. Multiple critical open items prevent acceptance: (1) The PSD load input in the production run encodes 7.5 g RMS versus the specified 9.0 g RMS — all reported margins are therefore non-conservative and invalid for pass/fail. (2) Conflicting material properties (E = 110 vs 114 GPa; σy = 880 vs 930 MPa) are unresolved and used inconsistently across margin calculations. (3) The 3rd natural frequency is underpredicted by 12.2% against the stated ±10% acceptance criterion, yet the summary slide incorrectly asserts compliance. (4) The production run input file has a hash mismatch against the version-controlled tag, breaking reproducibility. (5) Bolt slip safety factor summary is internally inconsistent (1.25 vs 1.4 depending on assumed friction). The report itself concludes results are preliminary and lists six mandatory open items to be resolved before CDR. Until those items are closed and the model is re-run with consistent, verified inputs and re-correlated against test data, the model does not meet the credibility requirements for structural qualification decisions.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
